--- a/artfynd/A 40071-2025 artfynd.xlsx
+++ b/artfynd/A 40071-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>78047552</v>
       </c>
       <c r="B2" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517141.0128146629</v>
+        <v>517141</v>
       </c>
       <c r="R2" t="n">
-        <v>6543229.130918685</v>
+        <v>6543229</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2017-05-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
